--- a/agent/1.6新增模组候选清单.xlsx
+++ b/agent/1.6新增模组候选清单.xlsx
@@ -407,18 +407,23 @@
         <x:v>原行</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="30" customHeight="1">
+    <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" s="3" t="str">
         <x:v>add-01</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
         <x:v>鞘翅槽位 / Elytra Slot</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>候选</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>原称 Curious Elytra；以原表 elytra-slot 项目链接定位。</x:v>
+      <x:c r="C5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">候选（过时）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原称 Curious Elytra；以原表 elytra-slot 项目链接定位。
+状态更新（2026-10-09）：Elytra Slot 6.4.4+1.20.1、Curios 5.14.1+1.20.1、Caelus 3.2.0+1.20.1 已入包及两服本地目录，待游戏测试。依据：0372110、3c21860及当前索引。</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" s="3" t="str">
         <x:v>https://www.mcmod.cn/class/3923.html
